--- a/artfynd/A 10694-2024 artfynd.xlsx
+++ b/artfynd/A 10694-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117016488</v>
+        <v>117016615</v>
       </c>
       <c r="B2" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539275</v>
+        <v>539187</v>
       </c>
       <c r="R2" t="n">
-        <v>6271075</v>
+        <v>6271103</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,62 +765,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Gunnarsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Robert Gunnarsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117016612</v>
+        <v>117018179</v>
       </c>
       <c r="B3" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539250</v>
+        <v>539133</v>
       </c>
       <c r="R3" t="n">
-        <v>6271133</v>
+        <v>6270971</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +850,11 @@
           <t>2024-05-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117016473</v>
+        <v>117016165</v>
       </c>
       <c r="B4" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,14 +910,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539240</v>
+        <v>539277</v>
       </c>
       <c r="R4" t="n">
-        <v>6271122</v>
+        <v>6271038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,11 +952,6 @@
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tio-tal plantor</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -974,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117016643</v>
+        <v>117016473</v>
       </c>
       <c r="B5" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,14 +1007,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539236</v>
+        <v>539240</v>
       </c>
       <c r="R5" t="n">
-        <v>6271121</v>
+        <v>6271122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1049,11 @@
           <t>2024-05-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tio-tal plantor</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1076,27 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117017274</v>
+        <v>117016488</v>
       </c>
       <c r="B6" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,17 +1109,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539221</v>
+        <v>539275</v>
       </c>
       <c r="R6" t="n">
-        <v>6271117</v>
+        <v>6271075</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,27 +1163,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Robert Gunnarsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Robert Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117017956</v>
+        <v>117016502</v>
       </c>
       <c r="B7" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,14 +1206,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539224</v>
+        <v>539278</v>
       </c>
       <c r="R7" t="n">
-        <v>6270951</v>
+        <v>6271117</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,12 +1275,7 @@
         <v>117016517</v>
       </c>
       <c r="B8" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,7 +1307,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1401,12 +1376,7 @@
         <v>117016571</v>
       </c>
       <c r="B9" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,7 +1404,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1500,15 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117017334</v>
+        <v>117016612</v>
       </c>
       <c r="B10" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,14 +1501,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539242</v>
+        <v>539250</v>
       </c>
       <c r="R10" t="n">
-        <v>6271124</v>
+        <v>6271133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,50 +1567,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117018179</v>
+        <v>117016643</v>
       </c>
       <c r="B11" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539133</v>
+        <v>539236</v>
       </c>
       <c r="R11" t="n">
-        <v>6270971</v>
+        <v>6271121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,11 +1640,6 @@
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1697,27 +1652,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117016502</v>
+        <v>117017189</v>
       </c>
       <c r="B12" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,14 +1695,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539278</v>
+        <v>539220</v>
       </c>
       <c r="R12" t="n">
-        <v>6271117</v>
+        <v>6271111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,15 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117018195</v>
+        <v>117017274</v>
       </c>
       <c r="B13" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,17 +1792,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539145</v>
+        <v>539221</v>
       </c>
       <c r="R13" t="n">
-        <v>6270965</v>
+        <v>6271117</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1901,27 +1846,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117017189</v>
+        <v>117017334</v>
       </c>
       <c r="B14" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,14 +1889,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östra Backabo (Östra Backabo), Sm</t>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539220</v>
+        <v>539242</v>
       </c>
       <c r="R14" t="n">
-        <v>6271111</v>
+        <v>6271124</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,6 +1952,200 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>117017956</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>539224</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6270951</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vissefjärda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>117018195</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Östra Backabo, Östra Backabo, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>539145</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6270965</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vissefjärda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10694-2024 artfynd.xlsx
+++ b/artfynd/A 10694-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117018179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016473</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016488</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016517</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016571</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016612</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117016643</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117017189</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1855,6 +1915,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117017274</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117017334</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,6 +2119,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117017956</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2146,8 +2221,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117018195</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>